--- a/Экономика_Кабинет_сотрудника_ЦП.xlsx
+++ b/Экономика_Кабинет_сотрудника_ЦП.xlsx
@@ -659,10 +659,6 @@
           <t>1С:Кабинет сотрудника — экономика продажи для Центра продаж (ЦП)</t>
         </is>
       </c>
-      <c r="B1" s="27" t="n"/>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -670,10 +666,6 @@
           <t>Маржинальный доход (МД) = Розничная цена − Закупочная цена (дилер). Из МД вычитается доля ЦСВ 30%. Остаток 70% — доход ЦП с одной продажи.</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n"/>
-      <c r="C2" s="27" t="n"/>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="27" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -707,10 +699,6 @@
           <t>Расчёт маржинального дохода и доли ЦП по вариантам продажи (все сроки лицензии)</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="29" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1542,20 +1530,15 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>Примечание: жёлтые ячейки — исходные цены из прайса (можно менять); зелёные — итоговый доход ЦП; оранжевые — доля ЦСВ. Доли ЦСВ/ЦП задаются в ячейках B5/D5.</t>
-        </is>
-      </c>
+      <c r="A51" s="25" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
+    <mergeCell ref="A50:E50"/>
     <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A50:E50"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A44:E44"/>

--- a/Экономика_Кабинет_сотрудника_ЦП.xlsx
+++ b/Экономика_Кабинет_сотрудника_ЦП.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Экономика ЦП" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Экономика ЦП'!$1:$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,18 +29,18 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -51,9 +49,9 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="11"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -71,8 +69,14 @@
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -86,12 +90,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D6E3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E3F0"/>
+        <fgColor rgb="00FFF8E7"/>
       </patternFill>
     </fill>
     <fill>
@@ -112,6 +121,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C65911"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -199,42 +228,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,42 +270,63 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -643,909 +692,1012 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника — экономика продажи для Центра продаж (ЦП)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Маржинальный доход (МД) = Розничная цена − Закупочная цена (дилер). Из МД вычитается доля ЦСВ 30%. Остаток 70% — доход ЦП с одной продажи.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Цены без НДС. Источник: прайс «цены кабинет сотрудника». Вариант 700 кабинетов = пакет 500 + пакет 200.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Доля ЦСВ</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>1С:Кабинет сотрудника — экономика продажи для ЦП и затраты ЦСВ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>МД = Розница − Закупка. Доля ЦСВ 30% от МД, ЦП 70% от МД. Затраты ЦСВ = часы по акции «Больше, чем кешбэк» × ставка линии консультаций. Акция и часы — при оплате пакета на 12 месяцев (до 100 кабинетов).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ПАРАМЕТРЫ</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Затраты ЦСВ по акции «Больше, чем кешбэк» (лицензия 12 мес.)</t>
+        </is>
+      </c>
+      <c r="H4" s="32" t="n"/>
+      <c r="I4" s="32" t="n"/>
+      <c r="J4" s="32" t="n"/>
+      <c r="K4" s="33" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Доля ЦСВ от МД</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Доля ЦП</t>
-        </is>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Акция «Больше, чем кешбэк»: при оплате Кабинета сотрудника начисляем клиенту часы на линию консультаций.
+10 каб. → +1 ч; 50 каб. → +3 ч; 100 каб. → +5 ч. Для 700 каб. акция не прописана — ячейки пустые.
+Ставка часа: 3 660 ₽; от 4 часов — 3 420 ₽; от 10 часов — 3 360 ₽.</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>10 кабинетов</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>50 кабинетов</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>100 кабинетов</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>700 кабинетов (500+200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Доля ЦП от МД</t>
+        </is>
+      </c>
+      <c r="B6" s="9">
         <f>1-B5</f>
         <v/>
       </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>Расчёт маржинального дохода и доли ЦП по вариантам продажи (все сроки лицензии)</t>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Часы на линию консультаций (акция)</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Ставка часа ЛК (&lt; 4 ч)</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>3660</v>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Ставка часа, руб.</t>
+        </is>
+      </c>
+      <c r="H7" s="17">
+        <f>IF(H6&gt;=10,$B$9,IF(H6&gt;=4,$B$8,$B$7))</f>
+        <v/>
+      </c>
+      <c r="I7" s="17">
+        <f>IF(I6&gt;=10,$B$9,IF(I6&gt;=4,$B$8,$B$7))</f>
+        <v/>
+      </c>
+      <c r="J7" s="17">
+        <f>IF(J6&gt;=10,$B$9,IF(J6&gt;=4,$B$8,$B$7))</f>
+        <v/>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Ставка часа ЛК (от 4 ч)</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>3420</v>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
+        <is>
+          <t>Затраты ЦСВ на часы, руб.</t>
+        </is>
+      </c>
+      <c r="H8" s="19">
+        <f>H6*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="19">
+        <f>I6*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f>J6*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Ставка часа ЛК (от 10 ч)</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Для 700 кабинетов акция не прописана — затраты не считаем. Ставка выбирается автоматически по числу часов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Расчёт маржинального дохода и доли ЦП / ЦСВ по вариантам продажи</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>Сводная таблица ЦСВ (продажа на 12 месяцев)</t>
+        </is>
+      </c>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="32" t="n"/>
+      <c r="K11" s="33" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Срок лицензии: 1 месяц</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n"/>
-      <c r="C8" s="30" t="n"/>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="33" t="n"/>
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>10 кабинетов</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>50 кабинетов</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>100 кабинетов</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>700 кабинетов (500+200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>10 кабинетов</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>50 кабинетов</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>100 кабинетов</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>700 кабинетов
 (500+200)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Состав (артикулы прайса)</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 10 на 1 месяц</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 50 на 1 месяц</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 100 на 1 месяц</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>500 на 1 месяц + 200 на 1 месяц</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Итого получено для ЦСВ (30% МД), руб.</t>
+        </is>
+      </c>
+      <c r="H13" s="24">
+        <f>B45</f>
+        <v/>
+      </c>
+      <c r="I13" s="24">
+        <f>C45</f>
+        <v/>
+      </c>
+      <c r="J13" s="24">
+        <f>D45</f>
+        <v/>
+      </c>
+      <c r="K13" s="24">
+        <f>E45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>пакет 10 на 1 месяц</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>пакет 50 на 1 месяц</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>пакет 100 на 1 месяц</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>пакет 500 + пакет 200 на 1 месяц</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
+        <is>
+          <t>Итого затрат ЦСВ (часы ЛК), руб.</t>
+        </is>
+      </c>
+      <c r="H14" s="26">
+        <f>H8</f>
+        <v/>
+      </c>
+      <c r="I14" s="26">
+        <f>I8</f>
+        <v/>
+      </c>
+      <c r="J14" s="26">
+        <f>J8</f>
+        <v/>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Розничная цена, руб. без НДС</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B15" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C15" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D15" s="27" t="n">
         <v>3000</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E15" s="27" t="n">
         <v>18600</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>Нетто ЦСВ (получено − затраты), руб.</t>
+        </is>
+      </c>
+      <c r="H15" s="29">
+        <f>H13-H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="29">
+        <f>I13-I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="29">
+        <f>J13-J14</f>
+        <v/>
+      </c>
+      <c r="K15" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Закупочная цена (дилер), руб. без НДС</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B16" s="27" t="n">
         <v>150</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C16" s="27" t="n">
         <v>750</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D16" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E16" s="27" t="n">
         <v>9300</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Маржинальный доход (МД), руб.</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>B11-B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="14">
-        <f>C11-C12</f>
-        <v/>
-      </c>
-      <c r="D13" s="14">
-        <f>D11-D12</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>E11-E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Цвета: жёлтый — вводные данные; оранжевый — доля/затраты ЦСВ; зелёный — доход ЦП; голубой — нетто ЦСВ. Цены без НДС из прайса «цены кабинет сотрудника». Акция — из image.png («Больше, чем кешбэк»).</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
+      <c r="H17" s="32" t="n"/>
+      <c r="I17" s="32" t="n"/>
+      <c r="J17" s="32" t="n"/>
+      <c r="K17" s="33" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>Доля ЦСВ (30% от МД), руб.</t>
         </is>
       </c>
-      <c r="B14" s="16">
-        <f>B13*$B$5</f>
-        <v/>
-      </c>
-      <c r="C14" s="16">
-        <f>C13*$B$5</f>
-        <v/>
-      </c>
-      <c r="D14" s="16">
-        <f>D13*$B$5</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>E13*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="B18" s="24">
+        <f>B17*$B$5</f>
+        <v/>
+      </c>
+      <c r="C18" s="24">
+        <f>C17*$B$5</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>D17*$B$5</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>E17*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Итого остаётся ЦП (70% от МД), руб.</t>
         </is>
       </c>
-      <c r="B15" s="18">
-        <f>B13*$D$5</f>
-        <v/>
-      </c>
-      <c r="C15" s="18">
-        <f>C13*$D$5</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
-        <f>D13*$D$5</f>
-        <v/>
-      </c>
-      <c r="E15" s="18">
-        <f>E13*$D$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="B19" s="35">
+        <f>B17*$B$6</f>
+        <v/>
+      </c>
+      <c r="C19" s="35">
+        <f>C17*$B$6</f>
+        <v/>
+      </c>
+      <c r="D19" s="35">
+        <f>D17*$B$6</f>
+        <v/>
+      </c>
+      <c r="E19" s="35">
+        <f>E17*$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Срок лицензии: 3 месяца</t>
         </is>
       </c>
-      <c r="B17" s="30" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="33" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>10 кабинетов</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>50 кабинетов</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>100 кабинетов</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>700 кабинетов
 (500+200)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Состав (артикулы прайса)</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 10 на 3 месяца</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 50 на 3 месяца</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 100 на 3 месяца</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>500 на 3 месяца + 200 на 3 месяца</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>пакет 10 на 3 месяца</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>пакет 50 на 3 месяца</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>пакет 100 на 3 месяца</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>пакет 500 + пакет 200 на 3 месяца</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Розничная цена, руб. без НДС</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B24" s="27" t="n">
         <v>885</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C24" s="27" t="n">
         <v>4425</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D24" s="27" t="n">
         <v>8850</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E24" s="27" t="n">
         <v>54750</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Закупочная цена (дилер), руб. без НДС</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B25" s="27" t="n">
         <v>443</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C25" s="27" t="n">
         <v>2213</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D25" s="27" t="n">
         <v>4425</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E25" s="27" t="n">
         <v>27375</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>Маржинальный доход (МД), руб.</t>
         </is>
       </c>
-      <c r="B22" s="14">
-        <f>B20-B21</f>
-        <v/>
-      </c>
-      <c r="C22" s="14">
-        <f>C20-C21</f>
-        <v/>
-      </c>
-      <c r="D22" s="14">
-        <f>D20-D21</f>
-        <v/>
-      </c>
-      <c r="E22" s="14">
-        <f>E20-E21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="B26" s="37">
+        <f>B24-B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="37">
+        <f>C24-C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="37">
+        <f>D24-D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="37">
+        <f>E24-E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>Доля ЦСВ (30% от МД), руб.</t>
         </is>
       </c>
-      <c r="B23" s="16">
-        <f>B22*$B$5</f>
-        <v/>
-      </c>
-      <c r="C23" s="16">
-        <f>C22*$B$5</f>
-        <v/>
-      </c>
-      <c r="D23" s="16">
-        <f>D22*$B$5</f>
-        <v/>
-      </c>
-      <c r="E23" s="16">
-        <f>E22*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="B27" s="24">
+        <f>B26*$B$5</f>
+        <v/>
+      </c>
+      <c r="C27" s="24">
+        <f>C26*$B$5</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>D26*$B$5</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>E26*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>Итого остаётся ЦП (70% от МД), руб.</t>
         </is>
       </c>
-      <c r="B24" s="18">
-        <f>B22*$D$5</f>
-        <v/>
-      </c>
-      <c r="C24" s="18">
-        <f>C22*$D$5</f>
-        <v/>
-      </c>
-      <c r="D24" s="18">
-        <f>D22*$D$5</f>
-        <v/>
-      </c>
-      <c r="E24" s="18">
-        <f>E22*$D$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="B28" s="35">
+        <f>B26*$B$6</f>
+        <v/>
+      </c>
+      <c r="C28" s="35">
+        <f>C26*$B$6</f>
+        <v/>
+      </c>
+      <c r="D28" s="35">
+        <f>D26*$B$6</f>
+        <v/>
+      </c>
+      <c r="E28" s="35">
+        <f>E26*$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Срок лицензии: 6 месяцев</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n"/>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="B30" s="32" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="32" t="n"/>
+      <c r="E30" s="33" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>10 кабинетов</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>50 кабинетов</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>100 кабинетов</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>700 кабинетов
 (500+200)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Состав (артикулы прайса)</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 10 на 6 месяцев</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 50 на 6 месяцев</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 100 на 6 месяцев</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>500 на 6 месяцев + 200 на 6 месяцев</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>пакет 10 на 6 месяцев</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>пакет 50 на 6 месяцев</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>пакет 100 на 6 месяцев</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>пакет 500 + пакет 200 на 6 месяцев</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Розничная цена, руб. без НДС</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B33" s="27" t="n">
         <v>1740</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C33" s="27" t="n">
         <v>8700</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D33" s="27" t="n">
         <v>17400</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="E33" s="27" t="n">
         <v>107400</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Закупочная цена (дилер), руб. без НДС</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B34" s="27" t="n">
         <v>870</v>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C34" s="27" t="n">
         <v>4350</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D34" s="27" t="n">
         <v>8700</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E34" s="27" t="n">
         <v>53700</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>Маржинальный доход (МД), руб.</t>
         </is>
       </c>
-      <c r="B31" s="14">
-        <f>B29-B30</f>
-        <v/>
-      </c>
-      <c r="C31" s="14">
-        <f>C29-C30</f>
-        <v/>
-      </c>
-      <c r="D31" s="14">
-        <f>D29-D30</f>
-        <v/>
-      </c>
-      <c r="E31" s="14">
-        <f>E29-E30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="B35" s="37">
+        <f>B33-B34</f>
+        <v/>
+      </c>
+      <c r="C35" s="37">
+        <f>C33-C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="37">
+        <f>D33-D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="37">
+        <f>E33-E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>Доля ЦСВ (30% от МД), руб.</t>
         </is>
       </c>
-      <c r="B32" s="16">
-        <f>B31*$B$5</f>
-        <v/>
-      </c>
-      <c r="C32" s="16">
-        <f>C31*$B$5</f>
-        <v/>
-      </c>
-      <c r="D32" s="16">
-        <f>D31*$B$5</f>
-        <v/>
-      </c>
-      <c r="E32" s="16">
-        <f>E31*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="B36" s="24">
+        <f>B35*$B$5</f>
+        <v/>
+      </c>
+      <c r="C36" s="24">
+        <f>C35*$B$5</f>
+        <v/>
+      </c>
+      <c r="D36" s="24">
+        <f>D35*$B$5</f>
+        <v/>
+      </c>
+      <c r="E36" s="24">
+        <f>E35*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t>Итого остаётся ЦП (70% от МД), руб.</t>
         </is>
       </c>
-      <c r="B33" s="18">
-        <f>B31*$D$5</f>
-        <v/>
-      </c>
-      <c r="C33" s="18">
-        <f>C31*$D$5</f>
-        <v/>
-      </c>
-      <c r="D33" s="18">
-        <f>D31*$D$5</f>
-        <v/>
-      </c>
-      <c r="E33" s="18">
-        <f>E31*$D$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="B37" s="35">
+        <f>B35*$B$6</f>
+        <v/>
+      </c>
+      <c r="C37" s="35">
+        <f>C35*$B$6</f>
+        <v/>
+      </c>
+      <c r="D37" s="35">
+        <f>D35*$B$6</f>
+        <v/>
+      </c>
+      <c r="E37" s="35">
+        <f>E35*$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Срок лицензии: 12 месяцев</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="32" t="n"/>
+      <c r="D39" s="32" t="n"/>
+      <c r="E39" s="33" t="n"/>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>10 кабинетов</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>50 кабинетов</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>100 кабинетов</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>700 кабинетов
 (500+200)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Состав (артикулы прайса)</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 10 на 12 месяцев</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 50 на 12 месяцев</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>1С:Кабинет сотрудника 100 на 12 месяцев</t>
-        </is>
-      </c>
-      <c r="E37" s="11" t="inlineStr">
-        <is>
-          <t>500 на 12 месяцев + 200 на 12 месяцев</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>пакет 10 на 12 месяцев</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>пакет 50 на 12 месяцев</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>пакет 100 на 12 месяцев</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
+        <is>
+          <t>пакет 500 + пакет 200 на 12 месяцев</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Розничная цена, руб. без НДС</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B42" s="27" t="n">
         <v>3360</v>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C42" s="27" t="n">
         <v>16800</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D42" s="27" t="n">
         <v>33600</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E42" s="27" t="n">
         <v>206400</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Закупочная цена (дилер), руб. без НДС</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B43" s="27" t="n">
         <v>1680</v>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C43" s="27" t="n">
         <v>8400</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D43" s="27" t="n">
         <v>16800</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E43" s="27" t="n">
         <v>103200</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="36" t="inlineStr">
         <is>
           <t>Маржинальный доход (МД), руб.</t>
         </is>
       </c>
-      <c r="B40" s="14">
-        <f>B38-B39</f>
-        <v/>
-      </c>
-      <c r="C40" s="14">
-        <f>C38-C39</f>
-        <v/>
-      </c>
-      <c r="D40" s="14">
-        <f>D38-D39</f>
-        <v/>
-      </c>
-      <c r="E40" s="14">
-        <f>E38-E39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="B44" s="37">
+        <f>B42-B43</f>
+        <v/>
+      </c>
+      <c r="C44" s="37">
+        <f>C42-C43</f>
+        <v/>
+      </c>
+      <c r="D44" s="37">
+        <f>D42-D43</f>
+        <v/>
+      </c>
+      <c r="E44" s="37">
+        <f>E42-E43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>Доля ЦСВ (30% от МД), руб.</t>
         </is>
       </c>
-      <c r="B41" s="16">
-        <f>B40*$B$5</f>
-        <v/>
-      </c>
-      <c r="C41" s="16">
-        <f>C40*$B$5</f>
-        <v/>
-      </c>
-      <c r="D41" s="16">
-        <f>D40*$B$5</f>
-        <v/>
-      </c>
-      <c r="E41" s="16">
-        <f>E40*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="B45" s="24">
+        <f>B44*$B$5</f>
+        <v/>
+      </c>
+      <c r="C45" s="24">
+        <f>C44*$B$5</f>
+        <v/>
+      </c>
+      <c r="D45" s="24">
+        <f>D44*$B$5</f>
+        <v/>
+      </c>
+      <c r="E45" s="24">
+        <f>E44*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>Итого остаётся ЦП (70% от МД), руб.</t>
         </is>
       </c>
-      <c r="B42" s="18">
-        <f>B40*$D$5</f>
-        <v/>
-      </c>
-      <c r="C42" s="18">
-        <f>C40*$D$5</f>
-        <v/>
-      </c>
-      <c r="D42" s="18">
-        <f>D40*$D$5</f>
-        <v/>
-      </c>
-      <c r="E42" s="18">
-        <f>E40*$D$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>Сводка: доход ЦП с одной продажи (лицензия на 12 месяцев) — основной сценарий</t>
-        </is>
-      </c>
-      <c r="B44" s="30" t="n"/>
-      <c r="C44" s="30" t="n"/>
-      <c r="D44" s="30" t="n"/>
-      <c r="E44" s="31" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>Вариант</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Розница, руб.</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>МД, руб.</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>ЦСВ 30%, руб.</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>ЦП 70%, руб.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>10 кабинетов</t>
-        </is>
-      </c>
-      <c r="B46" s="21">
-        <f>B38</f>
-        <v/>
-      </c>
-      <c r="C46" s="22">
-        <f>B40</f>
-        <v/>
-      </c>
-      <c r="D46" s="23">
-        <f>B41</f>
-        <v/>
-      </c>
-      <c r="E46" s="24">
-        <f>B42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>50 кабинетов</t>
-        </is>
-      </c>
-      <c r="B47" s="21">
-        <f>C38</f>
-        <v/>
-      </c>
-      <c r="C47" s="22">
-        <f>C40</f>
-        <v/>
-      </c>
-      <c r="D47" s="23">
-        <f>C41</f>
-        <v/>
-      </c>
-      <c r="E47" s="24">
-        <f>C42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>100 кабинетов</t>
-        </is>
-      </c>
-      <c r="B48" s="21">
-        <f>D38</f>
-        <v/>
-      </c>
-      <c r="C48" s="22">
-        <f>D40</f>
-        <v/>
-      </c>
-      <c r="D48" s="23">
-        <f>D41</f>
-        <v/>
-      </c>
-      <c r="E48" s="24">
-        <f>D42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>700 кабинетов (500+200)</t>
-        </is>
-      </c>
-      <c r="B49" s="21">
-        <f>E38</f>
-        <v/>
-      </c>
-      <c r="C49" s="22">
-        <f>E40</f>
-        <v/>
-      </c>
-      <c r="D49" s="23">
-        <f>E41</f>
-        <v/>
-      </c>
-      <c r="E49" s="24">
-        <f>E42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Примечание: жёлтые ячейки — исходные цены из прайса (можно менять); зелёные — итоговый доход ЦП; оранжевые — доля ЦСВ. Доли ЦСВ/ЦП задаются в ячейках B5/D5.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="25" t="n"/>
+      <c r="B46" s="35">
+        <f>B44*$B$6</f>
+        <v/>
+      </c>
+      <c r="C46" s="35">
+        <f>C44*$B$6</f>
+        <v/>
+      </c>
+      <c r="D46" s="35">
+        <f>D44*$B$6</f>
+        <v/>
+      </c>
+      <c r="E46" s="35">
+        <f>E44*$B$6</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="13">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C5:E9"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>